--- a/prospection/prospects_974_yeba.xlsx
+++ b/prospection/prospects_974_yeba.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Synthèse" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prospects 974'!$A$1:$O$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prospects 974'!$A$1:$P$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sous-traitance OF'!$A$1:$M$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -629,6 +630,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>• Sous-traitance : depuis la réforme, un organisme qui sous-traite une action CPF doit faire appel à un sous-traitant certifié Qualiopi au-delà de 72 000 € de CA (source : certiforma.fr / centre-inffo.fr). Votre Qualiopi est donc un argument direct. Exclus à votre demande : Beforma, Tetranergy, ICCI, Endémia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>• OPCO « probable » : déduit de la convention collective habituelle du secteur ; à confirmer avec l'entreprise.</t>
         </is>
@@ -645,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:P107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -663,6 +671,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -741,6 +750,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Remarque vérifiée</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -766,7 +780,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>3 rue Cité Jasmin, 97400</t>
+          <t>3 rue Cité Jasmin ou 20 rue Saint-Jacques, 97400 (sources divergentes) ; bureau secondaire à Saint-Pierre</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -794,6 +808,11 @@
           <t>https://www.annuaireavocats.fr/cabinets/droit-des-affaires/saint-denis-la-reunion ; https://gery-avocats-associes.fr/</t>
         </is>
       </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>Adresse à confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -851,6 +870,7 @@
           <t>https://www.annuaireavocats.fr/cabinets/droit-des-affaires/saint-denis-la-reunion ; https://gery-avocats-associes.fr/</t>
         </is>
       </c>
+      <c r="P3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -904,6 +924,7 @@
           <t>https://www.annuaireavocats.fr/cabinets/droit-des-affaires/saint-denis-la-reunion ; https://gery-avocats-associes.fr/</t>
         </is>
       </c>
+      <c r="P4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -953,6 +974,7 @@
           <t>https://www.annuaireavocats.fr/cabinets/droit-des-affaires/saint-denis-la-reunion ; https://gery-avocats-associes.fr/</t>
         </is>
       </c>
+      <c r="P5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1010,6 +1032,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/assurances-courtiers ; https://www.assurco-assurance-reunion.fr/ ; https://www.courtierassurances.re/ ; https://www.cea-assurances.fr/nos-agences/agence-reunion/</t>
         </is>
       </c>
+      <c r="P6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1043,7 +1066,11 @@
           <t>02 62 94 13 65</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>direction@assurco.re</t>
+        </is>
+      </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>https://www.assurco-assurance-reunion.fr/</t>
@@ -1068,7 +1095,12 @@
       <c r="N7" s="5" t="inlineStr"/>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/assurances-courtiers ; https://www.assurco-assurance-reunion.fr/ ; https://www.courtierassurances.re/ ; https://www.cea-assurances.fr/nos-agences/agence-reunion/</t>
+          <t>Recherche web 05/10/2026 (email direction@assurco.re cité avec le téléphone 0262941365) ; https://www.assurco-assurance-reunion.fr/</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>4 agences sur l'île</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1110,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CEA Réunion</t>
+          <t>CEA Réunion – Centre d'études d'assurances</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1125,9 +1157,10 @@
       <c r="N8" s="5" t="inlineStr"/>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/assurances-courtiers ; https://www.assurco-assurance-reunion.fr/ ; https://www.courtierassurances.re/ ; https://www.cea-assurances.fr/nos-agences/agence-reunion/</t>
-        </is>
-      </c>
+          <t>https://www.pappers.fr/entreprise/439031857 ; https://www.cea-assurances.fr/nos-agences/agence-reunion/</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1189,6 +1222,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/assurances-courtiers ; https://www.assurco-assurance-reunion.fr/ ; https://www.courtierassurances.re/ ; https://www.cea-assurances.fr/nos-agences/agence-reunion/</t>
         </is>
       </c>
+      <c r="P9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1246,6 +1280,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/assurances-courtiers ; https://www.assurco-assurance-reunion.fr/ ; https://www.courtierassurances.re/ ; https://www.cea-assurances.fr/nos-agences/agence-reunion/</t>
         </is>
       </c>
+      <c r="P10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1303,6 +1338,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/assurances-courtiers ; https://www.assurco-assurance-reunion.fr/ ; https://www.courtierassurances.re/ ; https://www.cea-assurances.fr/nos-agences/agence-reunion/</t>
         </is>
       </c>
+      <c r="P11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1360,6 +1396,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/assurances-courtiers ; https://www.assurco-assurance-reunion.fr/ ; https://www.courtierassurances.re/ ; https://www.cea-assurances.fr/nos-agences/agence-reunion/</t>
         </is>
       </c>
+      <c r="P12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1367,7 +1404,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Amarris (cabinet de Saint-Denis)</t>
+          <t>AS Expertise Comptable</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1383,14 +1420,14 @@
           <t>Saint-Denis</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>41 rue Monthion, 97400</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>https://www.amarris-contact.fr/cabinets/expert-comptable-a-saint-denis-de-la-reunion/</t>
-        </is>
-      </c>
+      <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Atlas</t>
@@ -1410,9 +1447,10 @@
       <c r="N13" s="5" t="inlineStr"/>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>Recherche web 05/10/2026 – fiches Pages Jaunes (pagesjaunes.fr/pros/53172001, 63020050, 05903597) et https://www.pagesjaunes.fr/annuaire/departement/reunion-974/expertise-comptable</t>
-        </is>
-      </c>
+          <t>https://fr.mappy.com/poi/5a6aa0500351d11fa08edb02 ; https://fr.mappy.com/poi/65e3e5aa00ef9c78bfaac72d</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1470,6 +1508,7 @@
           <t>Recherche web 05/10/2026 – fiches Pages Jaunes (pagesjaunes.fr/pros/53172001, 63020050, 05903597) et https://www.pagesjaunes.fr/annuaire/departement/reunion-974/expertise-comptable</t>
         </is>
       </c>
+      <c r="P14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1527,6 +1566,11 @@
           <t>Recherche web 05/10/2026 – fiches Pages Jaunes (pagesjaunes.fr/pros/53172001, 63020050, 05903597) et https://www.pagesjaunes.fr/annuaire/departement/reunion-974/expertise-comptable</t>
         </is>
       </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>20 à 49 salariés : bonne taille pour un intra</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1552,7 +1596,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>42 rue Jules Olivier, 97400</t>
+          <t>42 rue Jules Olivier ou 64 rue Roland Garros, 97400 (sources divergentes)</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -1577,7 +1621,12 @@
       <c r="N16" s="5" t="inlineStr"/>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>Recherche web 05/10/2026 – fiches Pages Jaunes (pagesjaunes.fr/pros/53172001, 63020050, 05903597) et https://www.pagesjaunes.fr/annuaire/departement/reunion-974/expertise-comptable</t>
+          <t>https://finalib.fr/expert/cabinet-ah-foune-et-associes-expert-comptable-saint-denis-a7eab0 ; https://www.pagesjaunes.fr/annuaire/departement/reunion-974/expertise-comptable</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>Adresse à confirmer au premier appel</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1682,7 @@
           <t>https://comptable-lesexpertsdusud.re/ ; https://demarchesadministratives.fr/expert-comptable/saint-pierre-97410</t>
         </is>
       </c>
+      <c r="P17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1690,6 +1740,7 @@
           <t>Recherche web 05/10/2026 – fiches Pages Jaunes (pagesjaunes.fr/pros/53172001, 63020050, 05903597) et https://www.pagesjaunes.fr/annuaire/departement/reunion-974/expertise-comptable</t>
         </is>
       </c>
+      <c r="P18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1747,6 +1798,7 @@
           <t>Recherche web 05/10/2026 – fiches Pages Jaunes (pagesjaunes.fr/pros/53172001, 63020050, 05903597) et https://www.pagesjaunes.fr/annuaire/departement/reunion-974/expertise-comptable</t>
         </is>
       </c>
+      <c r="P19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1804,6 +1856,7 @@
           <t>Recherche web 05/10/2026 – fiches Pages Jaunes (pagesjaunes.fr/pros/53172001, 63020050, 05903597) et https://www.pagesjaunes.fr/annuaire/departement/reunion-974/expertise-comptable</t>
         </is>
       </c>
+      <c r="P20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1865,6 +1918,7 @@
           <t>https://comptable-lesexpertsdusud.re/ ; https://demarchesadministratives.fr/expert-comptable/saint-pierre-97410</t>
         </is>
       </c>
+      <c r="P21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1872,12 +1926,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Getim</t>
+          <t>Medon &amp; Associés</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Immobilier</t>
+          <t>Expertise comptable</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
@@ -1890,28 +1944,24 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>4 avenue de la Victoire, 97400</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>02 62 21 12 61</t>
-        </is>
-      </c>
+          <t>21 rue Jules Auber, 97400</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>https://www.getim.com/</t>
+          <t>https://www.hlb.global/reunion</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>À vérifier</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Annonces, comptes rendus de visite, réponses aux mandants : l'IA au service de l'agence, dans les règles RGPD.</t>
+          <t>Vos collaborateurs saisissent-ils des données clients dans ChatGPT ? Formation IA + RGPD + charte d'usage, prise en charge OPCO Atlas.</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1923,7 +1973,12 @@
       <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>https://www.orpi.com/mvsnord/ ; https://www.getim.com/ ; https://isautier.re/ ; https://www.sixiemeavenue.com/agences/saint-denis974/ ; https://kaze-immobilier.fr/</t>
+          <t>https://www.pappers.fr/entreprise/451726152 ; https://finalib.fr/expert/medon-associes-expert-comptable-saint-denis-51ae12</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>En procédure de sauvegarde depuis le 08/02/2026 : budget formation probablement gelé, pas prioritaire</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1988,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Guy Hoquet Saint-Denis</t>
+          <t>Valentis Conseil &amp; Audit</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Immobilier</t>
+          <t>Expertise comptable</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
@@ -1951,32 +2006,20 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>13 rue Charles Gounod, 97400</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>02 62 41 66 00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>saintdenis@guyhoquet.re</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>https://la-reunion-saint-denis.guy-hoquet.com/</t>
-        </is>
-      </c>
+          <t>22 chemin Dufourg les Bas, 97400</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>À vérifier</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Annonces, comptes rendus de visite, réponses aux mandants : l'IA au service de l'agence, dans les règles RGPD.</t>
+          <t>Vos collaborateurs saisissent-ils des données clients dans ChatGPT ? Formation IA + RGPD + charte d'usage, prise en charge OPCO Atlas.</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -1988,9 +2031,10 @@
       <c r="N23" s="5" t="inlineStr"/>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>https://la-reunion-saint-denis.guy-hoquet.com/mon-agence ; https://la-reunion-saint-pierre.guy-hoquet.com/mon-agence</t>
-        </is>
-      </c>
+          <t>https://fr.mappy.com/poi/5a6aa0500351d11fa08edb02 ; https://fr.mappy.com/poi/65e3e5aa00ef9c78bfaac72d</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1998,7 +2042,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Guy Hoquet Saint-Pierre</t>
+          <t>Getim</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2011,27 +2055,23 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Saint-Pierre</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>78 bis bd Hubert Delisle, 97410</t>
+          <t>4 avenue de la Victoire, 97400 (+ agence à Saint-Pierre)</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>02 62 27 90 90</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>saintpierre@guyhoquet.re</t>
-        </is>
-      </c>
+          <t>02 62 21 12 61</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>https://la-reunion-saint-pierre.guy-hoquet.com/</t>
+          <t>https://www.getim.com/</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2053,7 +2093,12 @@
       <c r="N24" s="5" t="inlineStr"/>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>https://la-reunion-saint-denis.guy-hoquet.com/mon-agence ; https://la-reunion-saint-pierre.guy-hoquet.com/mon-agence</t>
+          <t>https://www.orpi.com/mvsnord/ ; https://www.getim.com/ ; https://isautier.re/ ; https://www.sixiemeavenue.com/agences/saint-denis974/ ; https://kaze-immobilier.fr/</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>Attention : un homonyme « Getim » en Algérie apparaît dans les recherches d'email, ne pas confondre</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2108,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Isautier Immobilier</t>
+          <t>Guy Hoquet Saint-Denis</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2081,18 +2126,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>11 rue Juliette Dodu, 97400</t>
+          <t>13 rue Charles Gounod, 97400</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>02 62 55 05 50</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>02 62 41 66 00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>saintdenis@guyhoquet.re</t>
+        </is>
+      </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>https://isautier.re/</t>
+          <t>https://la-reunion-saint-denis.guy-hoquet.com/</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2114,9 +2163,10 @@
       <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>https://www.orpi.com/mvsnord/ ; https://www.getim.com/ ; https://isautier.re/ ; https://www.sixiemeavenue.com/agences/saint-denis974/ ; https://kaze-immobilier.fr/</t>
-        </is>
-      </c>
+          <t>https://la-reunion-saint-denis.guy-hoquet.com/mon-agence ; https://la-reunion-saint-pierre.guy-hoquet.com/mon-agence</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -2124,7 +2174,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Kaze Immobilier</t>
+          <t>Guy Hoquet Saint-Pierre</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2137,15 +2187,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>78 bis bd Hubert Delisle, 97410</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>02 62 27 90 90</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>saintpierre@guyhoquet.re</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>https://kaze-immobilier.fr/</t>
+          <t>https://la-reunion-saint-pierre.guy-hoquet.com/</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2167,9 +2229,10 @@
       <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>https://www.orpi.com/mvsnord/ ; https://www.getim.com/ ; https://isautier.re/ ; https://www.sixiemeavenue.com/agences/saint-denis974/ ; https://kaze-immobilier.fr/</t>
-        </is>
-      </c>
+          <t>https://la-reunion-saint-denis.guy-hoquet.com/mon-agence ; https://la-reunion-saint-pierre.guy-hoquet.com/mon-agence</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2177,7 +2240,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Orpi MVS (Saint-Denis, Saint-Gilles, Saint-Pierre)</t>
+          <t>Isautier Immobilier</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2195,18 +2258,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>55 rue Labourdonnais, 97400</t>
+          <t>11 rue Juliette Dodu, 97400</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>02 62 51 74 74</t>
+          <t>02 62 55 05 50</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>https://www.orpi.com/mvsnord/</t>
+          <t>https://isautier.re/</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2231,6 +2294,7 @@
           <t>https://www.orpi.com/mvsnord/ ; https://www.getim.com/ ; https://isautier.re/ ; https://www.sixiemeavenue.com/agences/saint-denis974/ ; https://kaze-immobilier.fr/</t>
         </is>
       </c>
+      <c r="P27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2238,7 +2302,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Sixième Avenue Saint-Denis</t>
+          <t>Kaze Immobilier</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2259,7 +2323,7 @@
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>https://www.sixiemeavenue.com/agences/saint-denis974/</t>
+          <t>https://kaze-immobilier.fr/</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2284,6 +2348,7 @@
           <t>https://www.orpi.com/mvsnord/ ; https://www.getim.com/ ; https://isautier.re/ ; https://www.sixiemeavenue.com/agences/saint-denis974/ ; https://kaze-immobilier.fr/</t>
         </is>
       </c>
+      <c r="P28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -2291,12 +2356,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>NOT'AVENIR Notaires</t>
+          <t>Orpi MVS (Saint-Denis, Saint-Gilles, Saint-Pierre)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Notariat</t>
+          <t>Immobilier</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
@@ -2304,33 +2369,33 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Saint-Paul</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>8 rue Évariste de Parny, 97460 (+ Saint-Denis : 66 rue Labourdonnais, 02 62 73 08 08)</t>
+          <t>55 rue Labourdonnais, 97400 (+ 103 rue du Général de Gaulle, Saint-Gilles ; 30 rue de la Cayenne, Saint-Pierre)</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>02 62 45 45 65</t>
+          <t>02 62 51 74 74</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>https://notavenir.notaires.fr/</t>
+          <t>https://www.orpi.com/mvs/</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>OPCO EP</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Secret professionnel + IA : quelles pratiques autorisées ? Formation et charte pour l'étude (OPCO EP).</t>
+          <t>Annonces, comptes rendus de visite, réponses aux mandants : l'IA au service de l'agence, dans les règles RGPD.</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2342,7 +2407,12 @@
       <c r="N29" s="5" t="inlineStr"/>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>https://notavenir.notaires.fr/ ; https://notaires-pasteur.notaires.fr/ ; https://chambre-reunion.notaires.fr/notaire/</t>
+          <t>https://www.orpi.com/mvsnord/ ; https://www.getim.com/ ; https://isautier.re/ ; https://www.sixiemeavenue.com/agences/saint-denis974/ ; https://kaze-immobilier.fr/</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>3 agences : proposer un intra commun</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2422,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Notaires Pasteur</t>
+          <t>Sixième Avenue Saint-Denis</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Notariat</t>
+          <t>Immobilier</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
@@ -2368,30 +2438,22 @@
           <t>Saint-Denis</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>44 rue Pasteur, 97400</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>02 62 90 14 14</t>
-        </is>
-      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>https://notaires-pasteur.notaires.fr/</t>
+          <t>https://www.sixiemeavenue.com/agences/saint-denis974/</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>OPCO EP</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Secret professionnel + IA : quelles pratiques autorisées ? Formation et charte pour l'étude (OPCO EP).</t>
+          <t>Annonces, comptes rendus de visite, réponses aux mandants : l'IA au service de l'agence, dans les règles RGPD.</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2403,9 +2465,10 @@
       <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>https://notavenir.notaires.fr/ ; https://notaires-pasteur.notaires.fr/ ; https://chambre-reunion.notaires.fr/notaire/</t>
-        </is>
-      </c>
+          <t>https://www.orpi.com/mvsnord/ ; https://www.getim.com/ ; https://isautier.re/ ; https://www.sixiemeavenue.com/agences/saint-denis974/ ; https://kaze-immobilier.fr/</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2413,7 +2476,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Office notarial Aubert et associés</t>
+          <t>NOT'AVENIR Notaires</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2426,21 +2489,25 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Saint-Pierre</t>
+          <t>Saint-Paul</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>32 rue Luc Lorion, 97453 Saint-Pierre Cedex</t>
+          <t>8 rue Évariste de Parny, 97460 (+ Saint-Denis : 66 rue Labourdonnais, 02 62 73 08 08)</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>02 62 25 00 89</t>
+          <t>02 62 45 45 65</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>https://notavenir.notaires.fr/</t>
+        </is>
+      </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>OPCO EP</t>
@@ -2463,6 +2530,7 @@
           <t>https://notavenir.notaires.fr/ ; https://notaires-pasteur.notaires.fr/ ; https://chambre-reunion.notaires.fr/notaire/</t>
         </is>
       </c>
+      <c r="P31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -2470,7 +2538,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Étude Gaudieux</t>
+          <t>Notaires Pasteur</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2488,16 +2556,20 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>62 bd du Chaudron, Centre d'affaires Cadjee, Bât. A, 9e ét., 97400</t>
+          <t>44 rue Pasteur, 97400</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>02 62 15 08 40</t>
+          <t>02 62 90 14 14</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
-      <c r="I32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>https://notaires-pasteur.notaires.fr/</t>
+        </is>
+      </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
           <t>OPCO EP</t>
@@ -2520,6 +2592,7 @@
           <t>https://notavenir.notaires.fr/ ; https://notaires-pasteur.notaires.fr/ ; https://chambre-reunion.notaires.fr/notaire/</t>
         </is>
       </c>
+      <c r="P32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2527,34 +2600,42 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ABCD Mobilier</t>
+          <t>Office notarial Aubert et associés</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Commerce de gros</t>
+          <t>Notariat</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>32 rue Luc Lorion, 97453 Saint-Pierre Cedex</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>02 62 25 00 89</t>
+        </is>
+      </c>
       <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>https://www.abcd-mobilier.fr/</t>
-        </is>
-      </c>
+      <c r="I33" s="4" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>AKTO</t>
+          <t>OPCO EP</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Devis, fiches produits, relances : 1 journée pour gagner du temps avec l'IA sans exposer vos données clients (OPCO AKTO).</t>
+          <t>Secret professionnel + IA : quelles pratiques autorisées ? Formation et charte pour l'étude (OPCO EP).</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2566,9 +2647,10 @@
       <c r="N33" s="5" t="inlineStr"/>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
-        </is>
-      </c>
+          <t>https://notavenir.notaires.fr/ ; https://notaires-pasteur.notaires.fr/ ; https://chambre-reunion.notaires.fr/notaire/</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2576,16 +2658,16 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Adéquation Mobilier</t>
+          <t>Étude Gaudieux</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Commerce de gros</t>
+          <t>Notariat</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -2594,20 +2676,24 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>30 route Piton Bois de Nèfles</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr"/>
+          <t>62 bd du Chaudron, Centre d'affaires Cadjee, Bât. A, 9e ét., 97400</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>02 62 15 08 40</t>
+        </is>
+      </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>AKTO</t>
+          <t>OPCO EP</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Devis, fiches produits, relances : 1 journée pour gagner du temps avec l'IA sans exposer vos données clients (OPCO AKTO).</t>
+          <t>Secret professionnel + IA : quelles pratiques autorisées ? Formation et charte pour l'étude (OPCO EP).</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2619,9 +2705,10 @@
       <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
-        </is>
-      </c>
+          <t>https://notavenir.notaires.fr/ ; https://notaires-pasteur.notaires.fr/ ; https://chambre-reunion.notaires.fr/notaire/</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -2629,7 +2716,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>BUROCA</t>
+          <t>ABCD Mobilier</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2640,19 +2727,15 @@
       <c r="D35" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Sainte-Marie</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>6 rue Concorde, Innovespace A03 Duparc, 97438</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abcd-mobilier.fr/</t>
+        </is>
+      </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -2675,6 +2758,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
         </is>
       </c>
+      <c r="P35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -2682,7 +2766,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>BUROLIKE</t>
+          <t>Adéquation Mobilier</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2695,12 +2779,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Sainte-Marie</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2 rue du Soleil, PAE La Mare, 97438</t>
+          <t>30 route Piton Bois de Nèfles</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
@@ -2728,6 +2812,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
         </is>
       </c>
+      <c r="P36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2735,7 +2820,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Blanche Entreprises</t>
+          <t>BUROCA</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2748,12 +2833,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Sainte-Marie</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2 route Rivière des Pluies</t>
+          <t>6 rue Concorde, Innovespace A03 Duparc, 97438</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -2781,6 +2866,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
         </is>
       </c>
+      <c r="P37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -2788,7 +2874,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Bureaux &amp; Objets Réunion</t>
+          <t>BUROLIKE</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2801,17 +2887,17 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Saint-Pierre</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr"/>
+          <t>Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>2 rue du Soleil, PAE La Mare, 97438</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>https://bureauxetobjets.com/</t>
-        </is>
-      </c>
+      <c r="I38" s="4" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -2834,6 +2920,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
         </is>
       </c>
+      <c r="P38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2841,7 +2928,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>CGF Distribution</t>
+          <t>Blanche Entreprises</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2854,10 +2941,14 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Le Port</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr"/>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>2 route Rivière des Pluies</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr"/>
@@ -2880,9 +2971,10 @@
       <c r="N39" s="5" t="inlineStr"/>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>https://fr.kompass.com/a/commerce-de-gros/81250/r/la-reunion/fr_04/ ; https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/alimentation-generale-gros</t>
-        </is>
-      </c>
+          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2890,7 +2982,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>FAREN SAS</t>
+          <t>Bureaux &amp; Objets Réunion</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2903,17 +2995,17 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Sainte-Marie</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>10 rue Soleil, 97438</t>
-        </is>
-      </c>
+          <t>Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>https://bureauxetobjets.com/</t>
+        </is>
+      </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -2933,9 +3025,10 @@
       <c r="N40" s="5" t="inlineStr"/>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>https://fr.kompass.com/a/commerce-de-gros/81250/r/la-reunion/fr_04/ ; https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/alimentation-generale-gros</t>
-        </is>
-      </c>
+          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2943,7 +3036,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Food Import Océan Indien</t>
+          <t>CGF Distribution</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2956,21 +3049,13 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Sainte-Marie</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>1 rue Général de Gaulle, 97438</t>
-        </is>
-      </c>
+          <t>Le Port</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>https://foodimport-oi.re/</t>
-        </is>
-      </c>
+      <c r="I41" s="4" t="inlineStr"/>
       <c r="J41" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -2990,9 +3075,10 @@
       <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>https://foodimport-oi.re/</t>
-        </is>
-      </c>
+          <t>https://fr.kompass.com/a/commerce-de-gros/81250/r/la-reunion/fr_04/ ; https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/alimentation-generale-gros</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -3000,7 +3086,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Offital (mobilier de bureau)</t>
+          <t>FAREN SAS</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3018,16 +3104,12 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>67 rue André Lardy, 97438</t>
+          <t>10 rue Soleil, 97438</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>https://offital.com/</t>
-        </is>
-      </c>
+      <c r="I42" s="4" t="inlineStr"/>
       <c r="J42" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -3047,9 +3129,10 @@
       <c r="N42" s="5" t="inlineStr"/>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
-        </is>
-      </c>
+          <t>https://fr.kompass.com/a/commerce-de-gros/81250/r/la-reunion/fr_04/ ; https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/alimentation-generale-gros</t>
+        </is>
+      </c>
+      <c r="P42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -3057,7 +3140,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>SDCOM</t>
+          <t>Food Import Océan Indien</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3068,11 +3151,23 @@
       <c r="D43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>1 rue Général de Gaulle, 97438</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>https://foodimport-oi.re/</t>
+        </is>
+      </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -3092,9 +3187,10 @@
       <c r="N43" s="5" t="inlineStr"/>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>https://fr.kompass.com/a/commerce-de-gros/81250/r/la-reunion/fr_04/ ; https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/alimentation-generale-gros</t>
-        </is>
-      </c>
+          <t>https://foodimport-oi.re/</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -3102,7 +3198,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>SIDISRUN</t>
+          <t>Offital (mobilier de bureau)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3120,12 +3216,16 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>PAE La Mare, 97438</t>
+          <t>67 rue André Lardy, 97438</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>https://offital.com/</t>
+        </is>
+      </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -3145,9 +3245,10 @@
       <c r="N44" s="5" t="inlineStr"/>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>https://fr.kompass.com/a/commerce-de-gros/81250/r/la-reunion/fr_04/ ; https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/alimentation-generale-gros</t>
-        </is>
-      </c>
+          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -3155,7 +3256,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Socodiex</t>
+          <t>SDCOM</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3193,6 +3294,7 @@
           <t>https://fr.kompass.com/a/commerce-de-gros/81250/r/la-reunion/fr_04/ ; https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/alimentation-generale-gros</t>
         </is>
       </c>
+      <c r="P45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -3200,7 +3302,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Somadis</t>
+          <t>SIDISRUN</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3213,12 +3315,12 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Sainte-Marie</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>98 rue de la République</t>
+          <t>PAE La Mare, 97438</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
@@ -3243,9 +3345,10 @@
       <c r="N46" s="5" t="inlineStr"/>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
-        </is>
-      </c>
+          <t>https://fr.kompass.com/a/commerce-de-gros/81250/r/la-reunion/fr_04/ ; https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/alimentation-generale-gros</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -3253,12 +3356,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>Socodiex</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Informatique / ESN</t>
+          <t>Commerce de gros</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
@@ -3268,19 +3371,15 @@
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>https://bnb.re/</t>
-        </is>
-      </c>
+      <c r="I47" s="4" t="inlineStr"/>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>AKTO</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Partenariat : vous déployez Copilot / M365, je forme les utilisateurs et sécurise RGPD / IA Act (OPCO Atlas).</t>
+          <t>Devis, fiches produits, relances : 1 journée pour gagner du temps avec l'IA sans exposer vos données clients (OPCO AKTO).</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -3292,9 +3391,10 @@
       <c r="N47" s="5" t="inlineStr"/>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>https://mdsi.re/groupe-mdsi-fiche-entreprise/ ; https://ecureuil-digital.re/societe-informatique-reunion/ ; https://bnb.re/</t>
-        </is>
-      </c>
+          <t>https://fr.kompass.com/a/commerce-de-gros/81250/r/la-reunion/fr_04/ ; https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/alimentation-generale-gros</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -3302,12 +3402,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Groupe MDSI</t>
+          <t>Somadis</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Informatique / ESN</t>
+          <t>Commerce de gros</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
@@ -3315,25 +3415,25 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Le Port</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr"/>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>98 rue de la République</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>https://mdsi.re/</t>
-        </is>
-      </c>
+      <c r="I48" s="4" t="inlineStr"/>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>AKTO</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Partenariat : vous déployez Copilot / M365, je forme les utilisateurs et sécurise RGPD / IA Act (OPCO Atlas).</t>
+          <t>Devis, fiches produits, relances : 1 journée pour gagner du temps avec l'IA sans exposer vos données clients (OPCO AKTO).</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
@@ -3345,9 +3445,10 @@
       <c r="N48" s="5" t="inlineStr"/>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>https://mdsi.re/groupe-mdsi-fiche-entreprise/ ; https://ecureuil-digital.re/societe-informatique-reunion/ ; https://bnb.re/</t>
-        </is>
-      </c>
+          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/mobilier-de-bureau ; https://offital.com/ ; https://bureauxetobjets.com/</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -3355,7 +3456,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Écureuil Digital</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3366,21 +3467,13 @@
       <c r="D49" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Saint-Denis</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>3 agences : Saint-Denis, Saint-Paul, Saint-Pierre</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr"/>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>https://ecureuil-digital.re/</t>
+          <t>https://bnb.re/</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3405,6 +3498,7 @@
           <t>https://mdsi.re/groupe-mdsi-fiche-entreprise/ ; https://ecureuil-digital.re/societe-informatique-reunion/ ; https://bnb.re/</t>
         </is>
       </c>
+      <c r="P49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -3412,34 +3506,38 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Alter Ego Océan Indien</t>
+          <t>Groupe MDSI</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Intérim &amp; recrutement</t>
+          <t>Informatique / ESN</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>4 agences sur l'île</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Le Port</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>https://mdsi.re/</t>
+        </is>
+      </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>AKTO</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Tri de CV par IA = haut risque IA Act (annexe III) : audit + formation de vos chargés de recrutement.</t>
+          <t>Partenariat : vous déployez Copilot / M365, je forme les utilisateurs et sécurise RGPD / IA Act (OPCO Atlas).</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -3451,9 +3549,10 @@
       <c r="N50" s="5" t="inlineStr"/>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/agences-d-interim-et-d-emploi ; http://www.974job.com/agences ; https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
-        </is>
-      </c>
+          <t>https://mdsi.re/groupe-mdsi-fiche-entreprise/ ; https://ecureuil-digital.re/societe-informatique-reunion/ ; https://bnb.re/</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -3461,12 +3560,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Axion</t>
+          <t>Écureuil Digital</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Intérim &amp; recrutement</t>
+          <t>Informatique / ESN</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
@@ -3479,20 +3578,24 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>30 rue Labourdonnais, 97400</t>
+          <t>3 agences : Saint-Denis, Saint-Paul, Saint-Pierre</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr"/>
-      <c r="I51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>https://ecureuil-digital.re/</t>
+        </is>
+      </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>AKTO</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Tri de CV par IA = haut risque IA Act (annexe III) : audit + formation de vos chargés de recrutement.</t>
+          <t>Partenariat : vous déployez Copilot / M365, je forme les utilisateurs et sécurise RGPD / IA Act (OPCO Atlas).</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -3504,9 +3607,10 @@
       <c r="N51" s="5" t="inlineStr"/>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/agences-d-interim-et-d-emploi ; http://www.974job.com/agences ; https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
-        </is>
-      </c>
+          <t>https://mdsi.re/groupe-mdsi-fiche-entreprise/ ; https://ecureuil-digital.re/societe-informatique-reunion/ ; https://bnb.re/</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -3514,7 +3618,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Hooter &amp; Event</t>
+          <t>Alter Ego Océan Indien</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3525,12 +3629,12 @@
       <c r="D52" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Saint-Denis</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>4 agences sur l'île</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr"/>
@@ -3556,6 +3660,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/agences-d-interim-et-d-emploi ; http://www.974job.com/agences ; https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
         </is>
       </c>
+      <c r="P52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -3563,7 +3668,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Profil Océan Indien</t>
+          <t>Axion</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3581,7 +3686,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>48 rue Général de Gaulle, 97400</t>
+          <t>30 rue Labourdonnais, 97400</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
@@ -3609,6 +3714,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/agences-d-interim-et-d-emploi ; http://www.974job.com/agences ; https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
         </is>
       </c>
+      <c r="P53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -3616,7 +3722,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Proman Gestion</t>
+          <t>Hooter &amp; Event</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -3632,11 +3738,7 @@
           <t>Saint-Denis</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>15 rue Pierre Aubert, Sainte-Clotilde, 97490</t>
-        </is>
-      </c>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr"/>
       <c r="I54" s="4" t="inlineStr"/>
@@ -3662,6 +3764,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/agences-d-interim-et-d-emploi ; http://www.974job.com/agences ; https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
         </is>
       </c>
+      <c r="P54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -3669,7 +3772,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Randstad Search Réunion</t>
+          <t>Profil Océan Indien</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3687,16 +3790,12 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>30 rue Labourdonnais, 97400</t>
+          <t>48 rue Général de Gaulle, 97400</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr"/>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
-        </is>
-      </c>
+      <c r="I55" s="4" t="inlineStr"/>
       <c r="J55" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -3719,6 +3818,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/agences-d-interim-et-d-emploi ; http://www.974job.com/agences ; https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
         </is>
       </c>
+      <c r="P55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -3726,7 +3826,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Réunion Emploi Intérim</t>
+          <t>Proman Gestion</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3744,7 +3844,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>45 av. Georges Brassens, Sainte-Clotilde, 97490</t>
+          <t>15 rue Pierre Aubert, Sainte-Clotilde, 97490</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
@@ -3772,6 +3872,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/agences-d-interim-et-d-emploi ; http://www.974job.com/agences ; https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
         </is>
       </c>
+      <c r="P56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -3779,7 +3880,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Service Intérim</t>
+          <t>Randstad Search Réunion</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3790,11 +3891,23 @@
       <c r="D57" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>30 rue Labourdonnais, 97400</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
+        </is>
+      </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -3817,6 +3930,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/agences-d-interim-et-d-emploi ; http://www.974job.com/agences ; https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
         </is>
       </c>
+      <c r="P57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -3824,12 +3938,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>DSG Transit Repiquet</t>
+          <t>Réunion Emploi Intérim</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Transport &amp; logistique</t>
+          <t>Intérim &amp; recrutement</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
@@ -3837,12 +3951,12 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Le Port</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>ZAC Belvédère, 17 rue Roland Hoareau, 97420</t>
+          <t>45 av. Georges Brassens, Sainte-Clotilde, 97490</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
@@ -3850,12 +3964,12 @@
       <c r="I58" s="4" t="inlineStr"/>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>OPCO Mobilités</t>
+          <t>AKTO</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Suivi d'expéditions, documents douaniers, emails clients : prompts métiers et règles de confidentialité (OPCO Mobilités).</t>
+          <t>Tri de CV par IA = haut risque IA Act (annexe III) : audit + formation de vos chargés de recrutement.</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
@@ -3867,9 +3981,10 @@
       <c r="N58" s="5" t="inlineStr"/>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>https://fr.kompass.com/s/transports-et-logistique/10/v/le-port/fr_04_974_97407/ ; https://www.pagesjaunes.fr/annuaire/le-port-974/transport-logistique</t>
-        </is>
-      </c>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/agences-d-interim-et-d-emploi ; http://www.974job.com/agences ; https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
+        </is>
+      </c>
+      <c r="P58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -3877,38 +3992,30 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>HOLDTRANS</t>
+          <t>Service Intérim</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Transport &amp; logistique</t>
+          <t>Intérim &amp; recrutement</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Le Port</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>2 rue Charles Darwin, 97420</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr"/>
       <c r="I59" s="4" t="inlineStr"/>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>OPCO Mobilités</t>
+          <t>AKTO</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Suivi d'expéditions, documents douaniers, emails clients : prompts métiers et règles de confidentialité (OPCO Mobilités).</t>
+          <t>Tri de CV par IA = haut risque IA Act (annexe III) : audit + formation de vos chargés de recrutement.</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -3920,9 +4027,10 @@
       <c r="N59" s="5" t="inlineStr"/>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>https://fr.kompass.com/s/transports-et-logistique/10/v/le-port/fr_04_974_97407/ ; https://www.pagesjaunes.fr/annuaire/le-port-974/transport-logistique</t>
-        </is>
-      </c>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/agences-d-interim-et-d-emploi ; http://www.974job.com/agences ; https://www.randstad.fr/nos-agences/randstad-search-reunion_2970/</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -3930,7 +4038,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Le Transit Norgat Fils (TNF)</t>
+          <t>DSG Transit Repiquet</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3948,7 +4056,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2 rue Émile Verhaeren, 97420</t>
+          <t>ZAC Belvédère, 17 rue Roland Hoareau, 97420</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
@@ -3976,6 +4084,7 @@
           <t>https://fr.kompass.com/s/transports-et-logistique/10/v/le-port/fr_04_974_97407/ ; https://www.pagesjaunes.fr/annuaire/le-port-974/transport-logistique</t>
         </is>
       </c>
+      <c r="P60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -3983,7 +4092,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>SNT – Société Nouvelle de Transport</t>
+          <t>HOLDTRANS</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3999,7 +4108,11 @@
           <t>Le Port</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>2 rue Charles Darwin, 97420</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr"/>
       <c r="I61" s="4" t="inlineStr"/>
@@ -4025,6 +4138,7 @@
           <t>https://fr.kompass.com/s/transports-et-logistique/10/v/le-port/fr_04_974_97407/ ; https://www.pagesjaunes.fr/annuaire/le-port-974/transport-logistique</t>
         </is>
       </c>
+      <c r="P61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -4032,7 +4146,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Schenker France (agence Réunion)</t>
+          <t>Le Transit Norgat Fils (TNF)</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4050,7 +4164,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>4 bis rue Paul Verlaine, 97420</t>
+          <t>2 rue Émile Verhaeren, 97420</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
@@ -4078,6 +4192,7 @@
           <t>https://fr.kompass.com/s/transports-et-logistique/10/v/le-port/fr_04_974_97407/ ; https://www.pagesjaunes.fr/annuaire/le-port-974/transport-logistique</t>
         </is>
       </c>
+      <c r="P62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -4085,7 +4200,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Sifa Réunion (Réunion Transit)</t>
+          <t>SNT – Société Nouvelle de Transport</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4101,11 +4216,7 @@
           <t>Le Port</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>ZI n°3, 30 rue Sully Prud'homme, 97420</t>
-        </is>
-      </c>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="4" t="inlineStr"/>
@@ -4131,6 +4242,7 @@
           <t>https://fr.kompass.com/s/transports-et-logistique/10/v/le-port/fr_04_974_97407/ ; https://www.pagesjaunes.fr/annuaire/le-port-974/transport-logistique</t>
         </is>
       </c>
+      <c r="P63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -4138,7 +4250,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Société Nouvelle Legarnisson (SNL)</t>
+          <t>Schenker France (agence Réunion)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4156,7 +4268,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>21 rue Camille Desmoulins, 97420</t>
+          <t>4 bis rue Paul Verlaine, 97420</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
@@ -4184,6 +4296,7 @@
           <t>https://fr.kompass.com/s/transports-et-logistique/10/v/le-port/fr_04_974_97407/ ; https://www.pagesjaunes.fr/annuaire/le-port-974/transport-logistique</t>
         </is>
       </c>
+      <c r="P64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -4191,7 +4304,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Transit Azélie C (TAC)</t>
+          <t>Sifa Réunion (Réunion Transit)</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4209,7 +4322,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>21 rue Léon de Lépervanche, 97420</t>
+          <t>ZI n°3, 30 rue Sully Prud'homme, 97420</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
@@ -4237,6 +4350,7 @@
           <t>https://fr.kompass.com/s/transports-et-logistique/10/v/le-port/fr_04_974_97407/ ; https://www.pagesjaunes.fr/annuaire/le-port-974/transport-logistique</t>
         </is>
       </c>
+      <c r="P65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -4244,42 +4358,38 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Air Voyages</t>
+          <t>Société Nouvelle Legarnisson (SNL)</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Agences de voyages</t>
+          <t>Transport &amp; logistique</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Le Port</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>7 rue Charles Gounod, 97400 (+ 40 rue des Bons Enfants, Saint-Pierre)</t>
+          <t>21 rue Camille Desmoulins, 97420</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>https://www.airvoyages.fr/nos-agences</t>
-        </is>
-      </c>
+      <c r="I66" s="4" t="inlineStr"/>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>À vérifier</t>
+          <t>OPCO Mobilités</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Programmes sur mesure, devis et emails clients en quelques minutes, sans fuite de données.</t>
+          <t>Suivi d'expéditions, documents douaniers, emails clients : prompts métiers et règles de confidentialité (OPCO Mobilités).</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
@@ -4291,9 +4401,10 @@
       <c r="N66" s="5" t="inlineStr"/>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
-        </is>
-      </c>
+          <t>https://fr.kompass.com/s/transports-et-logistique/10/v/le-port/fr_04_974_97407/ ; https://www.pagesjaunes.fr/annuaire/le-port-974/transport-logistique</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -4301,25 +4412,25 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Bluesky</t>
+          <t>Transit Azélie C (TAC)</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Agences de voyages</t>
+          <t>Transport &amp; logistique</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Le Port</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>74 rue Juliette Dodu, 97400</t>
+          <t>21 rue Léon de Lépervanche, 97420</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
@@ -4327,12 +4438,12 @@
       <c r="I67" s="4" t="inlineStr"/>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>À vérifier</t>
+          <t>OPCO Mobilités</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Programmes sur mesure, devis et emails clients en quelques minutes, sans fuite de données.</t>
+          <t>Suivi d'expéditions, documents douaniers, emails clients : prompts métiers et règles de confidentialité (OPCO Mobilités).</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
@@ -4344,9 +4455,10 @@
       <c r="N67" s="5" t="inlineStr"/>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
-        </is>
-      </c>
+          <t>https://fr.kompass.com/s/transports-et-logistique/10/v/le-port/fr_04_974_97407/ ; https://www.pagesjaunes.fr/annuaire/le-port-974/transport-logistique</t>
+        </is>
+      </c>
+      <c r="P67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -4354,7 +4466,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Euro Voyages (Selectour)</t>
+          <t>Air Voyages</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4372,14 +4484,14 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>34 rue Issop Ravate, 97400</t>
+          <t>7 rue Charles Gounod, 97400 (+ 40 rue des Bons Enfants, Saint-Pierre)</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="4" t="inlineStr"/>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
+          <t>https://www.airvoyages.fr/nos-agences</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -4404,6 +4516,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
         </is>
       </c>
+      <c r="P68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -4411,7 +4524,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Havas Voyages Réunion</t>
+          <t>Bluesky</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -4429,7 +4542,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>114 rue Juliette Dodu, 97400</t>
+          <t>74 rue Juliette Dodu, 97400</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
@@ -4457,6 +4570,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
         </is>
       </c>
+      <c r="P69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -4464,7 +4578,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Marines Voyages</t>
+          <t>Euro Voyages (Selectour)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -4477,17 +4591,21 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Saint-Pierre</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>1 boulevard Bank, 97410</t>
+          <t>34 rue Issop Ravate, 97400</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
       <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
+        </is>
+      </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
           <t>À vérifier</t>
@@ -4510,6 +4628,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
         </is>
       </c>
+      <c r="P70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -4517,7 +4636,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Odyssée</t>
+          <t>Havas Voyages Réunion</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -4535,7 +4654,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>56 rue Jules Auber, 97400</t>
+          <t>114 rue Juliette Dodu, 97400</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
@@ -4563,6 +4682,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
         </is>
       </c>
+      <c r="P71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -4570,7 +4690,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Transcontinents</t>
+          <t>Marines Voyages</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -4583,12 +4703,12 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Saint-Pierre</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>248 rue du Maréchal Leclerc, 97400 (+ 18 bd Hubert Delisle, Saint-Pierre)</t>
+          <t>1 boulevard Bank, 97410</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
@@ -4616,6 +4736,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
         </is>
       </c>
+      <c r="P72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -4623,7 +4744,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Voyages Réunion</t>
+          <t>Odyssée</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -4636,12 +4757,12 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Saint-Pierre</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>C. Cial Grand Large, allée Petit Paris, 97410</t>
+          <t>56 rue Jules Auber, 97400</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
@@ -4669,6 +4790,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
         </is>
       </c>
+      <c r="P73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -4676,7 +4798,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Yes We Can Travel</t>
+          <t>Transcontinents</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -4694,7 +4816,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>5 rue Charles Gounod, 97400</t>
+          <t>248 rue du Maréchal Leclerc, 97400 (+ 18 bd Hubert Delisle, Saint-Pierre)</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
@@ -4722,6 +4844,7 @@
           <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
         </is>
       </c>
+      <c r="P74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -4729,12 +4852,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Automobiles Réunion SN – Renault / Dacia</t>
+          <t>Voyages Réunion</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Agences de voyages</t>
         </is>
       </c>
       <c r="D75" s="4" t="n">
@@ -4742,12 +4865,12 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Le Port</t>
+          <t>Saint-Pierre</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>ZAC 2000, 15 rue Charles Darwin, 97420</t>
+          <t>C. Cial Grand Large, allée Petit Paris, 97410</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
@@ -4755,12 +4878,12 @@
       <c r="I75" s="4" t="inlineStr"/>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>OPCO Mobilités</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Relances clients, annonces VO, réponses aux avis : l'IA pour vos équipes commerciales et après-vente (OPCO Mobilités).</t>
+          <t>Programmes sur mesure, devis et emails clients en quelques minutes, sans fuite de données.</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
@@ -4772,9 +4895,10 @@
       <c r="N75" s="5" t="inlineStr"/>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>https://www.reunion-directory.com/professions/automobile-concessions-agents-.html ; https://www.pagesjaunes.fr/pros/07476950</t>
-        </is>
-      </c>
+          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
+        </is>
+      </c>
+      <c r="P75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -4782,12 +4906,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Bamytrucks (Mercedes-Benz Trucks, Iveco, DAF)</t>
+          <t>Yes We Can Travel</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Agences de voyages</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
@@ -4795,21 +4919,25 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Le Port</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr"/>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>5 rue Charles Gounod, 97400</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr"/>
       <c r="I76" s="4" t="inlineStr"/>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>OPCO Mobilités</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>Relances clients, annonces VO, réponses aux avis : l'IA pour vos équipes commerciales et après-vente (OPCO Mobilités).</t>
+          <t>Programmes sur mesure, devis et emails clients en quelques minutes, sans fuite de données.</t>
         </is>
       </c>
       <c r="L76" s="5" t="inlineStr">
@@ -4821,9 +4949,10 @@
       <c r="N76" s="5" t="inlineStr"/>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>https://www.reunion-directory.com/professions/automobile-concessions-agents-.html ; https://www.pagesjaunes.fr/pros/07476950</t>
-        </is>
-      </c>
+          <t>https://www.pagesjaunes.fr/annuaire/departement/la-reunion-974/agences-de-voyages ; https://www.airvoyages.fr/nos-agences ; https://www.selectour.com/agence/la-reunion/saint-denis/euro-voyages/13703</t>
+        </is>
+      </c>
+      <c r="P76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -4831,7 +4960,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>CAT (Nissan, Seat, Honda, Opel…)</t>
+          <t>Automobiles Réunion SN – Renault / Dacia</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -4844,10 +4973,14 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr"/>
+          <t>Le Port</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>ZAC 2000, 15 rue Charles Darwin, 97420</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr"/>
       <c r="I77" s="4" t="inlineStr"/>
@@ -4873,6 +5006,7 @@
           <t>https://www.reunion-directory.com/professions/automobile-concessions-agents-.html ; https://www.pagesjaunes.fr/pros/07476950</t>
         </is>
       </c>
+      <c r="P77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -4880,7 +5014,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CMM Automobiles (groupe CFAO) – Toyota, Ford, Volvo</t>
+          <t>Bamytrucks (Mercedes-Benz Trucks, Iveco, DAF)</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -4896,11 +5030,7 @@
           <t>Le Port</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>4 chemin des Anglais, 97420 (+ 4 chemin du Grand Canal, Saint-Denis)</t>
-        </is>
-      </c>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="4" t="inlineStr"/>
       <c r="I78" s="4" t="inlineStr"/>
@@ -4926,6 +5056,7 @@
           <t>https://www.reunion-directory.com/professions/automobile-concessions-agents-.html ; https://www.pagesjaunes.fr/pros/07476950</t>
         </is>
       </c>
+      <c r="P78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -4933,7 +5064,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Hyundai Réunion</t>
+          <t>CAT (Nissan, Seat, Honda, Opel…)</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -4975,6 +5106,7 @@
           <t>https://www.reunion-directory.com/professions/automobile-concessions-agents-.html ; https://www.pagesjaunes.fr/pros/07476950</t>
         </is>
       </c>
+      <c r="P79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -4982,7 +5114,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>JS Auto 974</t>
+          <t>CMM Automobiles (groupe CFAO) – Toyota, Ford, Volvo</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4993,15 +5125,19 @@
       <c r="D80" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Le Port</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>4 chemin des Anglais, 97420 (+ 4 chemin du Grand Canal, Saint-Denis)</t>
+        </is>
+      </c>
       <c r="G80" s="4" t="inlineStr"/>
       <c r="H80" s="4" t="inlineStr"/>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>https://www.jsauto974.com/</t>
-        </is>
-      </c>
+      <c r="I80" s="4" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr">
         <is>
           <t>OPCO Mobilités</t>
@@ -5024,6 +5160,7 @@
           <t>https://www.reunion-directory.com/professions/automobile-concessions-agents-.html ; https://www.pagesjaunes.fr/pros/07476950</t>
         </is>
       </c>
+      <c r="P80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -5031,7 +5168,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Leal Réunion (BMW, Mini)</t>
+          <t>Hyundai Réunion</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -5073,6 +5210,7 @@
           <t>https://www.reunion-directory.com/professions/automobile-concessions-agents-.html ; https://www.pagesjaunes.fr/pros/07476950</t>
         </is>
       </c>
+      <c r="P81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -5080,38 +5218,34 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Archipel (résidence hôtelière)</t>
+          <t>JS Auto 974</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Hôtellerie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>Saint-Paul</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>Saint-Gilles-les-Bains</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="inlineStr"/>
       <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jsauto974.com/</t>
+        </is>
+      </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>AKTO</t>
+          <t>OPCO Mobilités</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>Réponses aux avis, emails multilingues, fiches séjour : l'IA pour vos équipes de réception (OPCO AKTO).</t>
+          <t>Relances clients, annonces VO, réponses aux avis : l'IA pour vos équipes commerciales et après-vente (OPCO Mobilités).</t>
         </is>
       </c>
       <c r="L82" s="5" t="inlineStr">
@@ -5123,9 +5257,10 @@
       <c r="N82" s="5" t="inlineStr"/>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
-        </is>
-      </c>
+          <t>https://www.reunion-directory.com/professions/automobile-concessions-agents-.html ; https://www.pagesjaunes.fr/pros/07476950</t>
+        </is>
+      </c>
+      <c r="P82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -5133,12 +5268,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Golden Tulip Sainte-Clotilde</t>
+          <t>Leal Réunion (BMW, Mini)</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Hôtellerie</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
@@ -5152,19 +5287,15 @@
       <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr"/>
-      <c r="I83" s="4" t="inlineStr">
-        <is>
-          <t>https://www.goldentulip.com/en-us/our-hotels/la-reunion/hotels-saint-denis/</t>
-        </is>
-      </c>
+      <c r="I83" s="4" t="inlineStr"/>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>AKTO</t>
+          <t>OPCO Mobilités</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Réponses aux avis, emails multilingues, fiches séjour : l'IA pour vos équipes de réception (OPCO AKTO).</t>
+          <t>Relances clients, annonces VO, réponses aux avis : l'IA pour vos équipes commerciales et après-vente (OPCO Mobilités).</t>
         </is>
       </c>
       <c r="L83" s="5" t="inlineStr">
@@ -5176,9 +5307,10 @@
       <c r="N83" s="5" t="inlineStr"/>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
-        </is>
-      </c>
+          <t>https://www.reunion-directory.com/professions/automobile-concessions-agents-.html ; https://www.pagesjaunes.fr/pros/07476950</t>
+        </is>
+      </c>
+      <c r="P83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -5186,7 +5318,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Hôtel Austral by Exsel</t>
+          <t>Archipel (résidence hôtelière)</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -5199,10 +5331,14 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr"/>
+          <t>Saint-Paul</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Gilles-les-Bains</t>
+        </is>
+      </c>
       <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr"/>
       <c r="I84" s="4" t="inlineStr"/>
@@ -5228,6 +5364,7 @@
           <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
         </is>
       </c>
+      <c r="P84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -5235,7 +5372,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Hôtel Exsel Créolia</t>
+          <t>Golden Tulip Sainte-Clotilde</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -5254,7 +5391,11 @@
       <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr"/>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.goldentulip.com/en-us/our-hotels/la-reunion/hotels-saint-denis/</t>
+        </is>
+      </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -5277,6 +5418,7 @@
           <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
         </is>
       </c>
+      <c r="P85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -5284,7 +5426,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Hôtel Exsel Ermitage</t>
+          <t>Hôtel Austral by Exsel</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -5297,14 +5439,10 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Saint-Paul</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>Saint-Gilles-les-Bains</t>
-        </is>
-      </c>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="inlineStr"/>
       <c r="H86" s="4" t="inlineStr"/>
       <c r="I86" s="4" t="inlineStr"/>
@@ -5330,6 +5468,7 @@
           <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
         </is>
       </c>
+      <c r="P86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -5337,7 +5476,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Le Boucan Canot</t>
+          <t>Hôtel Exsel Créolia</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -5350,14 +5489,10 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Saint-Paul</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>Boucan Canot</t>
-        </is>
-      </c>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="inlineStr"/>
       <c r="H87" s="4" t="inlineStr"/>
       <c r="I87" s="4" t="inlineStr"/>
@@ -5383,6 +5518,7 @@
           <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
         </is>
       </c>
+      <c r="P87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -5390,7 +5526,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Le Juliette Dodu</t>
+          <t>Hôtel Exsel Ermitage</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -5403,10 +5539,14 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr"/>
+          <t>Saint-Paul</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Gilles-les-Bains</t>
+        </is>
+      </c>
       <c r="G88" s="4" t="inlineStr"/>
       <c r="H88" s="4" t="inlineStr"/>
       <c r="I88" s="4" t="inlineStr"/>
@@ -5432,6 +5572,7 @@
           <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
         </is>
       </c>
+      <c r="P88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -5439,7 +5580,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Le Récif Saint-Gilles (groupe LUX*)</t>
+          <t>Le Boucan Canot</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -5457,7 +5598,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Saint-Gilles-les-Bains</t>
+          <t>Boucan Canot</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
@@ -5485,6 +5626,7 @@
           <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
         </is>
       </c>
+      <c r="P89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -5492,7 +5634,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Radisson Hôtel Saint-Denis</t>
+          <t>Le Juliette Dodu</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -5534,6 +5676,7 @@
           <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
         </is>
       </c>
+      <c r="P90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -5541,7 +5684,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Relais de l'Hermitage</t>
+          <t>Le Récif Saint-Gilles (groupe LUX*)</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -5564,11 +5707,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr"/>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>https://www.relais-hermitage-saintgilles.fr/en/</t>
-        </is>
-      </c>
+      <c r="I91" s="4" t="inlineStr"/>
       <c r="J91" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -5591,6 +5730,7 @@
           <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
         </is>
       </c>
+      <c r="P91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -5598,7 +5738,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Tama Hôtel</t>
+          <t>Radisson Hôtel Saint-Denis</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -5611,14 +5751,10 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Saint-Paul</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>Saint-Gilles-les-Bains</t>
-        </is>
-      </c>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="inlineStr"/>
       <c r="H92" s="4" t="inlineStr"/>
       <c r="I92" s="4" t="inlineStr"/>
@@ -5644,6 +5780,7 @@
           <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
         </is>
       </c>
+      <c r="P92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -5651,7 +5788,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Tropic Appart Hôtel</t>
+          <t>Relais de l'Hermitage</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -5674,7 +5811,11 @@
       </c>
       <c r="G93" s="4" t="inlineStr"/>
       <c r="H93" s="4" t="inlineStr"/>
-      <c r="I93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.relais-hermitage-saintgilles.fr/en/</t>
+        </is>
+      </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
           <t>AKTO</t>
@@ -5697,6 +5838,7 @@
           <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
         </is>
       </c>
+      <c r="P93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -5704,30 +5846,38 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Brasserie Dalons</t>
+          <t>Tama Hôtel</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Agroalimentaire</t>
+          <t>Hôtellerie</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Paul</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Gilles-les-Bains</t>
+        </is>
+      </c>
       <c r="G94" s="4" t="inlineStr"/>
       <c r="H94" s="4" t="inlineStr"/>
       <c r="I94" s="4" t="inlineStr"/>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>OCAPIAT</t>
+          <t>AKTO</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Qualité, traçabilité, documents réglementaires : l'IA pour les fonctions support (OPCO OCAPIAT).</t>
+          <t>Réponses aux avis, emails multilingues, fiches séjour : l'IA pour vos équipes de réception (OPCO AKTO).</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
@@ -5739,9 +5889,10 @@
       <c r="N94" s="5" t="inlineStr"/>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>https://fr.wikipedia.org/wiki/Association_pour_le_d%C3%A9veloppement_industriel_de_La_R%C3%A9union ; https://adir.re/</t>
-        </is>
-      </c>
+          <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
+        </is>
+      </c>
+      <c r="P94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -5749,30 +5900,38 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Distillerie Chatel</t>
+          <t>Tropic Appart Hôtel</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Agroalimentaire</t>
+          <t>Hôtellerie</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Paul</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Gilles-les-Bains</t>
+        </is>
+      </c>
       <c r="G95" s="4" t="inlineStr"/>
       <c r="H95" s="4" t="inlineStr"/>
       <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>OCAPIAT</t>
+          <t>AKTO</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Qualité, traçabilité, documents réglementaires : l'IA pour les fonctions support (OPCO OCAPIAT).</t>
+          <t>Réponses aux avis, emails multilingues, fiches séjour : l'IA pour vos équipes de réception (OPCO AKTO).</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
@@ -5784,9 +5943,10 @@
       <c r="N95" s="5" t="inlineStr"/>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>https://fr.wikipedia.org/wiki/Association_pour_le_d%C3%A9veloppement_industriel_de_La_R%C3%A9union ; https://adir.re/</t>
-        </is>
-      </c>
+          <t>https://www.reunion.fr/organisez/vos-activites/le-tour-de-l-ile-de-la-reunion/les-etapes-incontournables/saint-denis/hotels-4-etoiles-saint-denis/ ; https://hotels.ile-delareunion.com/fr/hotels-3-etoiles/</t>
+        </is>
+      </c>
+      <c r="P95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -5794,7 +5954,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Distillerie Rivière du Mât</t>
+          <t>Brasserie Dalons</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -5832,6 +5992,7 @@
           <t>https://fr.wikipedia.org/wiki/Association_pour_le_d%C3%A9veloppement_industriel_de_La_R%C3%A9union ; https://adir.re/</t>
         </is>
       </c>
+      <c r="P96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -5839,7 +6000,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Groupe Cilam</t>
+          <t>Distillerie Chatel</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -5877,6 +6038,7 @@
           <t>https://fr.wikipedia.org/wiki/Association_pour_le_d%C3%A9veloppement_industriel_de_La_R%C3%A9union ; https://adir.re/</t>
         </is>
       </c>
+      <c r="P97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -5884,7 +6046,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Mascarin</t>
+          <t>Distillerie Rivière du Mât</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -5922,6 +6084,7 @@
           <t>https://fr.wikipedia.org/wiki/Association_pour_le_d%C3%A9veloppement_industriel_de_La_R%C3%A9union ; https://adir.re/</t>
         </is>
       </c>
+      <c r="P98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -5929,7 +6092,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Ovocoop</t>
+          <t>Groupe Cilam</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -5967,6 +6130,7 @@
           <t>https://fr.wikipedia.org/wiki/Association_pour_le_d%C3%A9veloppement_industriel_de_La_R%C3%A9union ; https://adir.re/</t>
         </is>
       </c>
+      <c r="P99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -5974,7 +6138,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Rhum Isautier / Ets Isautier</t>
+          <t>Mascarin</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -6012,6 +6176,7 @@
           <t>https://fr.wikipedia.org/wiki/Association_pour_le_d%C3%A9veloppement_industriel_de_La_R%C3%A9union ; https://adir.re/</t>
         </is>
       </c>
+      <c r="P100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -6019,38 +6184,30 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>ABC Pro Bati</t>
+          <t>Ovocoop</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>BTP</t>
+          <t>Agroalimentaire</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>Le Port</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>3 allée Zélindor</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr"/>
       <c r="I101" s="4" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Constructys</t>
+          <t>OCAPIAT</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Devis, mémoires techniques d'appels d'offres, comptes rendus de chantier : l'IA pour les conducteurs de travaux (OPCO Constructys).</t>
+          <t>Qualité, traçabilité, documents réglementaires : l'IA pour les fonctions support (OPCO OCAPIAT).</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
@@ -6062,9 +6219,10 @@
       <c r="N101" s="5" t="inlineStr"/>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>https://www.pappers.fr/recherche/ville/st-denis-4/construction-btp/6 ; https://fr.kompass.com/a/entreprises-de-batiment/71100/r/la-reunion/fr_04/</t>
-        </is>
-      </c>
+          <t>https://fr.wikipedia.org/wiki/Association_pour_le_d%C3%A9veloppement_industriel_de_La_R%C3%A9union ; https://adir.re/</t>
+        </is>
+      </c>
+      <c r="P101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -6072,34 +6230,30 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>BBOI</t>
+          <t>Rhum Isautier / Ets Isautier</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>BTP</t>
+          <t>Agroalimentaire</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>Le Port</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
       <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="inlineStr"/>
       <c r="H102" s="4" t="inlineStr"/>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Constructys</t>
+          <t>OCAPIAT</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Devis, mémoires techniques d'appels d'offres, comptes rendus de chantier : l'IA pour les conducteurs de travaux (OPCO Constructys).</t>
+          <t>Qualité, traçabilité, documents réglementaires : l'IA pour les fonctions support (OPCO OCAPIAT).</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr">
@@ -6111,9 +6265,10 @@
       <c r="N102" s="5" t="inlineStr"/>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>https://www.pappers.fr/recherche/ville/st-denis-4/construction-btp/6 ; https://fr.kompass.com/a/entreprises-de-batiment/71100/r/la-reunion/fr_04/</t>
-        </is>
-      </c>
+          <t>https://fr.wikipedia.org/wiki/Association_pour_le_d%C3%A9veloppement_industriel_de_La_R%C3%A9union ; https://adir.re/</t>
+        </is>
+      </c>
+      <c r="P102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -6121,7 +6276,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Luciano Construction</t>
+          <t>ABC Pro Bati</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -6134,12 +6289,12 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Saint-Pierre</t>
+          <t>Le Port</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>6 ruelle Manciet</t>
+          <t>3 allée Zélindor</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
@@ -6167,6 +6322,7 @@
           <t>https://www.pappers.fr/recherche/ville/st-denis-4/construction-btp/6 ; https://fr.kompass.com/a/entreprises-de-batiment/71100/r/la-reunion/fr_04/</t>
         </is>
       </c>
+      <c r="P103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -6174,7 +6330,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>SMBTP – Société Maçonnerie BTP</t>
+          <t>BBOI</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -6187,14 +6343,10 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Saint-Pierre</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>13 impasse Sinaman</t>
-        </is>
-      </c>
+          <t>Le Port</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr"/>
       <c r="G104" s="4" t="inlineStr"/>
       <c r="H104" s="4" t="inlineStr"/>
       <c r="I104" s="4" t="inlineStr"/>
@@ -6220,6 +6372,7 @@
           <t>https://www.pappers.fr/recherche/ville/st-denis-4/construction-btp/6 ; https://fr.kompass.com/a/entreprises-de-batiment/71100/r/la-reunion/fr_04/</t>
         </is>
       </c>
+      <c r="P104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -6227,7 +6380,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Tile Rénovation</t>
+          <t>Luciano Construction</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -6240,12 +6393,12 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Saint-Pierre</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>63 rue Félix Guyon</t>
+          <t>6 ruelle Manciet</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
@@ -6273,11 +6426,120 @@
           <t>https://www.pappers.fr/recherche/ville/st-denis-4/construction-btp/6 ; https://fr.kompass.com/a/entreprises-de-batiment/71100/r/la-reunion/fr_04/</t>
         </is>
       </c>
+      <c r="P105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>SMBTP – Société Maçonnerie BTP</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>BTP</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>13 impasse Sinaman</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" s="4" t="inlineStr"/>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>Constructys</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>Devis, mémoires techniques d'appels d'offres, comptes rendus de chantier : l'IA pour les conducteurs de travaux (OPCO Constructys).</t>
+        </is>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="inlineStr"/>
+      <c r="N106" s="5" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/recherche/ville/st-denis-4/construction-btp/6 ; https://fr.kompass.com/a/entreprises-de-batiment/71100/r/la-reunion/fr_04/</t>
+        </is>
+      </c>
+      <c r="P106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Tile Rénovation</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>BTP</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>63 rue Félix Guyon</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr"/>
+      <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="inlineStr"/>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>Constructys</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>Devis, mémoires techniques d'appels d'offres, comptes rendus de chantier : l'IA pour les conducteurs de travaux (OPCO Constructys).</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="M107" s="6" t="inlineStr"/>
+      <c r="N107" s="5" t="inlineStr"/>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/recherche/ville/st-denis-4/construction-btp/6 ; https://fr.kompass.com/a/entreprises-de-batiment/71100/r/la-reunion/fr_04/</t>
+        </is>
+      </c>
+      <c r="P107" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O105"/>
+  <autoFilter ref="A1:P107"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"À qualifier,À contacter,Contacté,RDV,Proposition,Client,Opposition RGPD,Perdu"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6766,14 +7028,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -6784,20 +7054,60 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Piste / contact public</t>
-        </is>
-      </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>Domaines</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Adresse</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Téléphone</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Site web</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi vous / action</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Priorité</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Date candidature</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -6806,303 +7116,3088 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>VIAgence</t>
+          <t>Honoris Educational Network</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>OF métropole vendant en 974</t>
+          <t>Maurice</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>contact@viagence.com · 01 79 35 52 37</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
+          <t>Organisme agréé MQA</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Soft skills, Microsoft Office, automatisation, data, marketing digital</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://honoris.ac.mu/mqa-approved-training-programmes-mauritius/</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Partenariat : formation IA éligible au remboursement HRDC jusqu'à 90 %</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Programme reçu par votre amie</t>
+      <c r="L2" s="6" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>https://honoris.ac.mu/mqa-approved-training-programmes-mauritius/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>AKADEMIA FORMATION (Saint-Denis)</t>
+          <t>SMFP – Société mahoraise de formation professionnelle</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>OF 974</t>
+          <t>Mayotte – Mamoudzou</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Annonce Indeed « formateur indépendant – Initiation à l'IA »</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+          <t>OF 976 (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Numérique (CléA), social</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Mamoudzou</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.smfp-site.fr/</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Numérique + IA à Mayotte (AAP France 2030 Mayotte ouvert jusqu'au 31/12/2026)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>https://fr.indeed.com/q-formateur-ia-l-la-r%C3%A9union-emplois.html</t>
+      <c r="L3" s="6" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.intercariforef.org/formations/societe-mahoraise-de-formation-professionnelle-smfp/organisme-39_216.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>ILOI – Institut de l'Image de l'Océan Indien</t>
+          <t>Senza Formations</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>OF 974</t>
+          <t>Métropole → 974</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Candidature spontanée (appel 2026-2027 clos le 24/09)</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+          <t>OF national, sessions à Saint-Denis</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>IA générative</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Sessions à Saint-Denis (28/09-28/10 et 30/11-30/12/2026)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://senza-formations.com/ville/saint-denis/formation-initiation-lintelligence-artificielle-ia</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Programme des sessions IA à Saint-Denis : il leur faut un formateur local</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Résultat de recherche e-marchespublics</t>
+      <c r="L4" s="6" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>https://senza-formations.com/ville/saint-denis/formation-initiation-lintelligence-artificielle-ia</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>GRETA Réunion</t>
+          <t>VIAgence</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Consulaire / public</t>
+          <t>Métropole → 974</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>IA générative RS 6776, 16-18/11/2026</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+          <t>OF qui vend dans le 974</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>32 rue de Paris, 92100 Boulogne-Billancourt</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>01 79 35 52 37</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>contact@viagence.com</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Vend du présentiel à Saint-Denis sans être implanté : proposez-vous comme formateur sur place (modèle d'email dans opportunites.md)</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>https://ftlvreunion.fr/en-ce-moment/news/formation-ia-generative-en-presentiel.html</t>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Programme reçu par votre amie</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>CCI Réunion</t>
+          <t>A'Venir</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Consulaire / public</t>
+          <t>Réunion</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Catalogue « IA et productivité »</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+          <t>OF 974 (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Passerelle IA</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://a-venir.re/</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Co-animation « Passerelle IA »</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>https://reunion.cci.fr/formation/166206/ia-et-productivite-outils-et-bonnes-pratiques</t>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>https://a-venir.re/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>IFR – Institut de Formation de la Réunion</t>
+          <t>CCI Réunion (+ CFA Campus Pro Saint-Pierre)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>OF 974</t>
+          <t>Réunion</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>« IA pour tous »</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+          <t>Consulaire</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>IA et productivité, commerce, vente, gestion</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>CFA : 65 rue du Père Lafosse, 97410 Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://reunion.cci.fr/formation/166206/ia-et-productivite-outils-et-bonnes-pratiques</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Catalogue « IA et productivité » + CFA commerce et vente : être référencé comme intervenant</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ifr-reunion.re/formation-ia-pour-tous/</t>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>https://reunion.cci.fr/se-former/ecolescentres-de-formations/liste-des-nos-ecoles-cfa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>A'Venir</t>
+          <t>CFA Disciplina</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>OF 974</t>
+          <t>Réunion</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>« Passerelle IA »</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Cherchait des formateurs vente indépendants</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>https://a-venir.re/</t>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/emploi/formateur/reunion/s20m22d974</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>BEFORMA</t>
+          <t>IFR – Institut de Formation de la Réunion</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>Réunion</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Modules IA apprentis</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>IA pour tous, commerce, informatique, communication digitale</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ifr-reunion.re/formation-ia-pour-tous/</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Module « IA + RGPD » en complément de « IA pour tous »</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Résultat de recherche Indeed</t>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ifr-reunion.re/formation-ia-pour-tous/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>AFPAR</t>
+          <t>JD Formations</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Consulaire / public</t>
+          <t>Réunion</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Parcours développeur IA (avec Simplon)</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>IA (ChatGPT), métiers</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jdformations.re/formation-ia-chatgpt-a-la-reunion-974/</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Formation IA par métier : proposez co-animation et module conformité</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>https://outremers360.com/bassin-indien-appli/la-reunion-une-premiere-formation-de-developpeur-en-intelligence-artificielle-pour-le-territoire</t>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jdformations.re/formation-ia-chatgpt-a-la-reunion-974/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Endémia Formation</t>
+          <t>Numeria</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
           <t>OF 974</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Candidature spontanée</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>IA, numérique</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.numeria-formation.re/formations-intelligence-artificielle/</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Organise des formations IA : proposez le volet RGPD / IA Act et du renfort de formateurs</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Résultat de recherche Indeed</t>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.numeria-formation.re/formations-intelligence-artificielle/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Réunion Prospectives Compétences (Carif-Oref)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Prescripteur public</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Information sur la formation (formanoo.org)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>02 62 83 00 40</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>contact@rpc.re</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rpc.re</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Faites référencer vos formations sur formanoo.org : visibilité auprès des prescripteurs</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>https://centre-inffo.fr/content/uploads/2024/06/depliant-reseaux-062024.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Sarl Laboratoire L &amp; M</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Management, comptabilité, numérique / cybersécurité, bureautique, vente (+ pâtisserie, HACCP)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>A publié des offres de formateurs en management, numérique et techniques de vente</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/emploi/formateur/reunion/s20m22d974</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>DCP Formation</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Le Tampon + Mayotte</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Réseau national, centres locaux</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Informatique, IA, management, RH, comptabilité</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>4 rue du Collège, Plaine des Cafres, 97418 Le Tampon (+ centre à Mamoudzou)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>https://dcpformation.fr/centre_de_formation/letampon-974/</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Affiche l'IA et le management, et un centre à Mayotte : 2 territoires possibles</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>https://dcpformation.fr/centre_de_formation/letampon-974/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Digitalys</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-André</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Soft skills, numérique</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>825 avenue des Mascareignes, 97440 Saint-André</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>02 62 73 83 52</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>contact@digitalysformation.fr</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Soft skills + numérique : votre double profil</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.capitecorpus.com/formation-communication-soft-skills/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>AKADEMIA FORMATION</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Denis</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Denis 97400</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Annonce « formateur indépendant – Initiation à l'IA » (7 h, présentiel) : candidatez si elle est encore en ligne</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>https://fr.indeed.com/q-formateur-ia-l-la-r%C3%A9union-emplois.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>CQFD Pro</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Denis</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue sur mesure en entreprise</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Formation sur mesure en entreprise : votre cœur de métier (vente, management, IA)</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/organisme-de-formation</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>GRETA Réunion (antenne Nord)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Denis</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Public (Éducation nationale)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>IA générative (RS 6776), tous domaines</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>https://ftlvreunion.fr/en-ce-moment/news/formation-ia-generative-en-presentiel.html</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Sessions IA du 16 au 18/11/2026 : vacations, module éthique et conformité</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>https://ftlvreunion.fr/en-ce-moment/news/formation-ia-generative-en-presentiel.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Educatis Forma</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Paul</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Négociation commerciale, assistanat</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Paul</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Recrutait des formateurs en négociation commerciale</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/emploi/formateur/reunion/s20m22d974</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Axam Formation</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Réseau national</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Informatique, bureautique, Power BI</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Pierre 974</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.axamformation.fr/informatique-saint-pierre/974</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Ajoutez l'IA à leur catalogue bureautique (Copilot, Gemini)</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.axamformation.fr/informatique-saint-pierre/974</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Agepac Formation</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Sainte-Clotilde</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>CFA / OF (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>BTS MCO, GPME, assurance</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Sainte-Clotilde, 97490 Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wizbii.com/company/agepac</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>BTS MCO = management commercial : vente, management, IA</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wizbii.com/company/agepac/job/assistant-commercial-gestion-et-relation-client-pro-pme-h-f-bts-mco-en-alternance-age13562</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Appavoo Business School</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Maurice</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Organisme agréé MQA</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Formation en entreprise</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>https://appavoo.com/education-n-training/</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Partenariat IA + vente / management</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>https://appavoo.com/education-n-training/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>IT Academy</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Maurice – Port-Louis</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Centre agréé MQA</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Certifications informatiques</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Port-Louis</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/itacademy.mu/</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Module IA appliquée</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/itacademy.mu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>ESCGM – École supérieure de commerce et de gestion de Mayotte</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Mayotte</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>École / OF</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Informatique, développeur web, commerce</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>IA et RGPD dans les cursus informatique et commerce</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.intercariforef.org/formations/cole-suprieur-de-commerce-et-de-gestion-de-mayotte.-escgm/organisme-39_225.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ITG Learning</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Métropole → 974</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>OF qui porte des formateurs indépendants</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>IA, tous domaines</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Déjà utilisé par un formateur IA du 974 pour la prise en charge OPCO. Vous avez votre propre Qualiopi : proposez-leur l'inverse, des missions en sous-traitance</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>https://jmberthelot.com/formation-intelligence-artificielle-la-reunion.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>CNFPT – délégation Réunion</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Public (agents territoriaux)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Formation des collectivités</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cnfpt.fr/se-former/suivre-formation/inscription-ligne/vos-interlocuteurs-formation-a-delegation-reunion/vos-contacts-a-delegation-reunion/reunion</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Les collectivités se forment à l'IA : se faire référencer comme intervenant</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cnfpt.fr/se-former/suivre-formation/inscription-ligne/vos-interlocuteurs-formation-a-delegation-reunion/vos-contacts-a-delegation-reunion/reunion</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Simplon (partenaire de l'AFPAR)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>OF national</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Développeur IA</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Module conformité IA Act / RGPD dans la formation développeur IA</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>https://outremers360.com/bassin-indien-appli/la-reunion-une-premiere-formation-de-developpeur-en-intelligence-artificielle-pour-le-territoire</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>AFPAR</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Réunion (4 centres)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Organisme régional</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>150 formations, parcours développeur IA</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Centres de Saint-André, Saint-Denis, Saint-Paul, Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>https://afpar.re/</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Intervenant « éthique, RGPD, IA Act » dans le parcours IA</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>https://afpar.re/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Envergure</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – La Possession</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>OF 974 (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Accompagnement de consultants indépendants</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>5 rue Justin Baptiste, 97419 La Possession</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Travaille avec des consultants indépendants : partenariat naturel</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/le-port-974/organisme-de-formation</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ILOI – Institut de l'Image de l'Océan Indien</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Le Port</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>École</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Audiovisuel, création numérique, IA</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Le Port</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Recrutait des formateurs externes 2026-2027 avec un module IA (clos le 24/09) : candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Résultat de recherche e-marchespublics.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>CFA Horizon Réunion</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Le Tampon</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>CFA (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Vente, commerce, marketing (Bac à Bac+3)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>4 boulevard Michel Debré, 97430 Le Tampon</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Vente + IA appliquée au commerce</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/pros/12005556</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Form'aou</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-André + Saint-Louis</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>OF / CFA</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Commerce, administration, coiffure</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Saint-André (+ centre à Saint-Louis)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Commerce et vente</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/emploi/formateur/reunion/s20m22d974</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Advance Formation &amp; Développement</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Benoît</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Soft skills</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Benoît</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mesenseignes.fr/advance-formation-developpement/5167-formation-soft-skills-a-lile-de-la-reunion-974/</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Soft skills : votre expertise historique</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mesenseignes.fr/advance-formation-developpement/5167-formation-soft-skills-a-lile-de-la-reunion-974/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Run Paye Formation</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Benoît</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Paie, gestion</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>55 rue Auguste de Villèle, 97470 Saint-Benoît</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>IA et RGPD pour les gestionnaires de paie (données sensibles)</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-benoit-974/formation-professionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>CFA de l'Université de La Réunion / FTLV</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Denis</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Public (université)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Tertiaire, numérique</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>2 rue Joseph Wetzell, 97400 Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>https://ftlvreunion.fr/</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Intervenant professionnel IA / RGPD en licence pro et formation continue</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>http://geolocalisation.onisep.fr/974-la-reunion/saint-denis/cfa/centre-de-formation-d-apprentis-de-l-universite-de-la-reunion-universite-de-la-reunion.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>EAFC – École académique de la formation continue</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Denis</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Public (académie)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>24 avenue Georges Brassens, 97400 Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>02 62 48 13 39</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Recrute des intervenants vacataires : dossier de candidature</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ac-reunion.fr/media/46832/download</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Develop'A Ou</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Leu</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>OF 974 (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Bureautique, informatique, accueil, petite enfance</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>5 chemin des Francisceas, 97425 Saint-Leu</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>IA dans les formations bureautique</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-leu-974/apprentissage-formation-professionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Ariane Formation</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Paul</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>OF 974 (Qualiopi depuis 2003)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>6 route de Savanna, 97460 Saint-Paul</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ariane-formation.re/</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ariane-formation.re/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Capital Formation</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Paul</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>OF 974 (Qualiopi, 20 ans)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue, bilan, apprentissage</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>171 Chaussée Royale, 1er étage, 97460 Saint-Paul</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Candidature : management, vente, IA</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-paul-974/formation-professionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>AREFIP</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>OF 974 (Qualiopi depuis l'origine)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Formation professionnelle, informatique, solutions RH</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>24 Cité de la Plaine, 97410 Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>02 62 96 19 79</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.arefip.fr/</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Informatique + RH : IA et RGPD pour les fonctions RH</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.arefip.fr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>CEFOR – Centre d'enseignement et de formation de la Réunion</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>BTS comptabilité et gestion</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>2 avenue Laurent Vergès, 97432 Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>IA pour la comptabilité et la gestion</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr"/>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>https://dossierappel.parcoursup.fr/Candidats/public/fiches/afficherFicheFormation?g_ta_cod=48130&amp;typeBac=0&amp;originePc=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>GEM Formation</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>OF / CFA (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Assistant de direction, formation continue, bilan, VAE</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>35 ter rue du Four à Chaux, 97410 Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gemformation974/</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>10 à 19 salariés ; modules IA bureautique pour assistants de direction</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-pierre-974/formation-professionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Success Formation</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>CFA / OF</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Assistant manager, assistant commercial, logistique</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Titres « assistant manager » et « commercial » : management et vente</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/emploi/formateur/reunion/s20m22d974</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Unicomp Computer Training Institute</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Maurice – Port-Louis</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Organisme agréé MQA</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Informatique</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>St Pierre, Port-Louis</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>https://unicomp.mu/</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Module IA appliquée</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>https://unicomp.mu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Forma Plus Consulting</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Mayotte</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>OF 976 (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Formation professionnelle</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/departement/mayotte-976/formation-professionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>CFPEI</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Mayotte – Mamoudzou</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>OF 976</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Emploi et insertion</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Mamoudzou</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/departement/mayotte-976/formation-professionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Forma Boost</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Mayotte – Mamoudzou</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>OF 976</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Formation professionnelle</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Mamoudzou</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/pros/61699180</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Mayotte Consulting et Formation</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Mayotte – Mamoudzou</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>OF 976</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>18 rue Zamantale, Kawéni, 97600 Mamoudzou</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/pros/55055224</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Boomerang Océan Indien</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Réseau d'insertion</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Confiance, stress, travail en équipe, codes de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>https://boomerang-oi.fr/</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Insertion + soft skills ; votre casquette de référent handicap compte</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>https://boomerang-oi.fr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ERFP – École régionale de la formation professionnelle</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Apprentissage, formation continue</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-denis-974/organisme-de-formation</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
           <t>ISFOI</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>OF 974</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Formation professionnelle</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>Candidature spontanée</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>À contacter</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="L51" s="6" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>Résultat de recherche Indeed</t>
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Inclus à Nous</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Soft skills en groupes</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inclusanous.re/groupes.html</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Soft skills, groupes de 10-12 personnes</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inclusanous.re/groupes.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Eximus Formation</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Est</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>OF 974 (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-andre-974/formation-professionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Cap Formation</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Le Port</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>OF 974 (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>4 rue François de Mahy, 97420 Le Port</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/pros/07769038</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/pros/07769038</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>ABC Formation Continue</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Denis</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Denis 97400</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.maformation.fr/centres/marque_abc-formation-continue_ville_saint-denis-97400.html</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.maformation.fr/centres/marque_abc-formation-continue_ville_saint-denis-97400.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>CFOR – Centre de formation Ouest Réunion</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Paul</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>OF 974 (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Présentiel et distanciel</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>11 rue Hôpital, 97460 Saint-Paul</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-paul-974/formation-professionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Arena Run</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>132 rue Victor le Vigoureux, 97410 Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr"/>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>https://fr.mappy.com/poi/589bb27b0351d167ec4d43a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>FRIC Formation</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>OF 974 (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>70 rue Suffren, 97410 Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>06 93 20 69 00</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-pierre-974/formation-professionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Réussir SARL</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>OF 974</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>10 bis chemin Maxime Rivière, 97410 Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr"/>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>https://fr.mappy.com/poi/589c0f910351d167ec4d6a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>SARL CAP'R HQS</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Réunion – Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>OF 974 (Qualiopi)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Formation continue</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>43B rue du Presbytère, 97410 Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>06 92 17 50 02</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Candidature spontanée</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr"/>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/annuaire/saint-pierre-974/formation-professionnelle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:M60"/>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"À contacter,Candidature envoyée,En discussion,Référencé,Mission obtenue,Sans suite"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7188,27 +10283,27 @@
         <v>1</v>
       </c>
       <c r="C4" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A4)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A4)</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A4,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A4,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A4,'Prospects 974'!$L$2:$L$105,"Contacté")+G4+F4+COUNTIFS('Prospects 974'!$C$2:$C$105,A4,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A4,'Prospects 974'!$L$2:$L$107,"Contacté")+G4+F4+COUNTIFS('Prospects 974'!$C$2:$C$107,A4,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A4,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A4,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G4" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A4,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A4,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H4" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A4,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A4,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7222,27 +10317,27 @@
         <v>1</v>
       </c>
       <c r="C5" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A5)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A5)</f>
         <v/>
       </c>
       <c r="D5" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A5,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A5,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E5" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A5,'Prospects 974'!$L$2:$L$105,"Contacté")+G5+F5+COUNTIFS('Prospects 974'!$C$2:$C$105,A5,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A5,'Prospects 974'!$L$2:$L$107,"Contacté")+G5+F5+COUNTIFS('Prospects 974'!$C$2:$C$107,A5,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F5" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A5,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A5,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G5" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A5,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A5,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H5" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A5,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A5,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7256,27 +10351,27 @@
         <v>1</v>
       </c>
       <c r="C6" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A6)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A6)</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A6,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A6,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A6,'Prospects 974'!$L$2:$L$105,"Contacté")+G6+F6+COUNTIFS('Prospects 974'!$C$2:$C$105,A6,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A6,'Prospects 974'!$L$2:$L$107,"Contacté")+G6+F6+COUNTIFS('Prospects 974'!$C$2:$C$107,A6,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A6,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A6,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G6" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A6,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A6,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H6" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A6,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A6,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7290,27 +10385,27 @@
         <v>1</v>
       </c>
       <c r="C7" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A7)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A7)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A7,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A7,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A7,'Prospects 974'!$L$2:$L$105,"Contacté")+G7+F7+COUNTIFS('Prospects 974'!$C$2:$C$105,A7,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A7,'Prospects 974'!$L$2:$L$107,"Contacté")+G7+F7+COUNTIFS('Prospects 974'!$C$2:$C$107,A7,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A7,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A7,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G7" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A7,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A7,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H7" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A7,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A7,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7324,27 +10419,27 @@
         <v>1</v>
       </c>
       <c r="C8" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A8)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A8)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A8,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A8,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A8,'Prospects 974'!$L$2:$L$105,"Contacté")+G8+F8+COUNTIFS('Prospects 974'!$C$2:$C$105,A8,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A8,'Prospects 974'!$L$2:$L$107,"Contacté")+G8+F8+COUNTIFS('Prospects 974'!$C$2:$C$107,A8,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A8,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A8,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G8" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A8,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A8,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H8" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A8,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A8,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7358,27 +10453,27 @@
         <v>2</v>
       </c>
       <c r="C9" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A9)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A9)</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A9,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A9,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A9,'Prospects 974'!$L$2:$L$105,"Contacté")+G9+F9+COUNTIFS('Prospects 974'!$C$2:$C$105,A9,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A9,'Prospects 974'!$L$2:$L$107,"Contacté")+G9+F9+COUNTIFS('Prospects 974'!$C$2:$C$107,A9,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A9,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A9,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G9" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A9,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A9,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H9" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A9,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A9,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7392,27 +10487,27 @@
         <v>2</v>
       </c>
       <c r="C10" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A10)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A10)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A10,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A10,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A10,'Prospects 974'!$L$2:$L$105,"Contacté")+G10+F10+COUNTIFS('Prospects 974'!$C$2:$C$105,A10,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A10,'Prospects 974'!$L$2:$L$107,"Contacté")+G10+F10+COUNTIFS('Prospects 974'!$C$2:$C$107,A10,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A10,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A10,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A10,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A10,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H10" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A10,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A10,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7426,27 +10521,27 @@
         <v>2</v>
       </c>
       <c r="C11" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A11)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A11)</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A11,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A11,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A11,'Prospects 974'!$L$2:$L$105,"Contacté")+G11+F11+COUNTIFS('Prospects 974'!$C$2:$C$105,A11,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A11,'Prospects 974'!$L$2:$L$107,"Contacté")+G11+F11+COUNTIFS('Prospects 974'!$C$2:$C$107,A11,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A11,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A11,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A11,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A11,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H11" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A11,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A11,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7460,27 +10555,27 @@
         <v>2</v>
       </c>
       <c r="C12" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A12)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A12)</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A12,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A12,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A12,'Prospects 974'!$L$2:$L$105,"Contacté")+G12+F12+COUNTIFS('Prospects 974'!$C$2:$C$105,A12,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A12,'Prospects 974'!$L$2:$L$107,"Contacté")+G12+F12+COUNTIFS('Prospects 974'!$C$2:$C$107,A12,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A12,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A12,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A12,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A12,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H12" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A12,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A12,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7494,27 +10589,27 @@
         <v>3</v>
       </c>
       <c r="C13" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A13)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A13)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A13,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A13,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E13" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A13,'Prospects 974'!$L$2:$L$105,"Contacté")+G13+F13+COUNTIFS('Prospects 974'!$C$2:$C$105,A13,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A13,'Prospects 974'!$L$2:$L$107,"Contacté")+G13+F13+COUNTIFS('Prospects 974'!$C$2:$C$107,A13,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A13,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A13,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G13" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A13,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A13,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H13" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A13,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A13,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7528,27 +10623,27 @@
         <v>3</v>
       </c>
       <c r="C14" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A14)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A14)</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A14,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A14,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A14,'Prospects 974'!$L$2:$L$105,"Contacté")+G14+F14+COUNTIFS('Prospects 974'!$C$2:$C$105,A14,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A14,'Prospects 974'!$L$2:$L$107,"Contacté")+G14+F14+COUNTIFS('Prospects 974'!$C$2:$C$107,A14,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A14,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A14,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G14" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A14,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A14,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H14" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A14,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A14,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7562,27 +10657,27 @@
         <v>3</v>
       </c>
       <c r="C15" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A15)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A15)</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A15,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A15,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E15" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A15,'Prospects 974'!$L$2:$L$105,"Contacté")+G15+F15+COUNTIFS('Prospects 974'!$C$2:$C$105,A15,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A15,'Prospects 974'!$L$2:$L$107,"Contacté")+G15+F15+COUNTIFS('Prospects 974'!$C$2:$C$107,A15,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F15" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A15,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A15,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G15" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A15,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A15,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H15" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A15,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A15,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7596,27 +10691,27 @@
         <v>4</v>
       </c>
       <c r="C16" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A16)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A16)</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A16,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A16,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A16,'Prospects 974'!$L$2:$L$105,"Contacté")+G16+F16+COUNTIFS('Prospects 974'!$C$2:$C$105,A16,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A16,'Prospects 974'!$L$2:$L$107,"Contacté")+G16+F16+COUNTIFS('Prospects 974'!$C$2:$C$107,A16,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A16,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A16,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G16" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A16,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A16,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H16" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A16,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A16,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
@@ -7630,27 +10725,27 @@
         <v>4</v>
       </c>
       <c r="C17" s="9">
-        <f>COUNTIF('Prospects 974'!$C$2:$C$105,A17)</f>
+        <f>COUNTIF('Prospects 974'!$C$2:$C$107,A17)</f>
         <v/>
       </c>
       <c r="D17" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A17,'Prospects 974'!$G$2:$G$105,"&lt;&gt;")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A17,'Prospects 974'!$G$2:$G$107,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E17" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A17,'Prospects 974'!$L$2:$L$105,"Contacté")+G17+F17+COUNTIFS('Prospects 974'!$C$2:$C$105,A17,'Prospects 974'!$L$2:$L$105,"Proposition")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A17,'Prospects 974'!$L$2:$L$107,"Contacté")+G17+F17+COUNTIFS('Prospects 974'!$C$2:$C$107,A17,'Prospects 974'!$L$2:$L$107,"Proposition")</f>
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A17,'Prospects 974'!$L$2:$L$105,"RDV")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A17,'Prospects 974'!$L$2:$L$107,"RDV")</f>
         <v/>
       </c>
       <c r="G17" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A17,'Prospects 974'!$L$2:$L$105,"Client")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A17,'Prospects 974'!$L$2:$L$107,"Client")</f>
         <v/>
       </c>
       <c r="H17" s="9">
-        <f>COUNTIFS('Prospects 974'!$C$2:$C$105,A17,'Prospects 974'!$L$2:$L$105,"Opposition RGPD")</f>
+        <f>COUNTIFS('Prospects 974'!$C$2:$C$107,A17,'Prospects 974'!$L$2:$L$107,"Opposition RGPD")</f>
         <v/>
       </c>
     </row>
